--- a/e7sa_4/outputs/codebook.xlsx
+++ b/e7sa_4/outputs/codebook.xlsx
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>7</v>
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
         <v>9</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F45" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
         <v>7</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
         <v>7</v>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F80" t="n">
         <v>229</v>
@@ -3101,7 +3101,7 @@
         <v>10</v>
       </c>
       <c r="F81" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
         <v>12</v>
       </c>
       <c r="F82" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F83" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
@@ -3221,7 +3221,7 @@
         <v>10</v>
       </c>
       <c r="F85" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F86" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F87" t="n">
         <v>31</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F88" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
         <v>5</v>
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" t="n">
         <v>5</v>
@@ -3817,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="F103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" t="n">
         <v>5</v>
@@ -4395,7 +4395,7 @@
         <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" t="n">
         <v>5</v>
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F124" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" t="n">
         <v>5</v>
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>1</v>
       </c>
       <c r="F132" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F138" t="n">
         <v>5</v>
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F139" t="n">
         <v>5</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F141" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -5242,10 +5242,10 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F145" t="n">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
@@ -5272,7 +5272,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F146" t="n">
         <v>35</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F147" t="n">
         <v>35</v>
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F148" t="n">
         <v>35</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F149" t="n">
         <v>35</v>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F150" t="n">
         <v>35</v>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F151" t="n">
         <v>35</v>
@@ -5452,7 +5452,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F152" t="n">
         <v>35</v>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F153" t="n">
         <v>35</v>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F154" t="n">
         <v>5</v>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F155" t="n">
         <v>5</v>
@@ -5648,7 +5648,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F158" t="n">
         <v>5</v>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F159" t="n">
         <v>5</v>
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F163" t="n">
         <v>5</v>
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F164" t="n">
         <v>5</v>
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F165" t="n">
         <v>5</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F168" t="n">
         <v>5</v>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F170" t="n">
         <v>5</v>
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F171" t="n">
         <v>5</v>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F172" t="n">
         <v>5</v>
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F174" t="n">
         <v>5</v>
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F175" t="n">
         <v>5</v>
@@ -6260,7 +6260,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F176" t="n">
         <v>5</v>
@@ -6532,7 +6532,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F184" t="n">
         <v>5</v>
@@ -6668,7 +6668,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F188" t="n">
         <v>5</v>
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F199" t="n">
         <v>5</v>
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F201" t="n">
         <v>5</v>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F203" t="n">
         <v>5</v>
@@ -7212,7 +7212,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F204" t="n">
         <v>5</v>
@@ -7246,7 +7246,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F205" t="n">
         <v>5</v>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F208" t="n">
         <v>5</v>
